--- a/public/assets/static/template/dudi-import-template.xlsx
+++ b/public/assets/static/template/dudi-import-template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>TEMPLATE IMPORT DATA DUDI</t>
   </si>
@@ -26,49 +26,46 @@
     <t>nama</t>
   </si>
   <si>
-    <t>bidang_usaha</t>
-  </si>
-  <si>
     <t>alamat</t>
   </si>
   <si>
-    <t>telepon</t>
-  </si>
-  <si>
-    <t>email</t>
+    <t>telp</t>
+  </si>
+  <si>
+    <t>pic</t>
+  </si>
+  <si>
+    <t>id_jurusan</t>
+  </si>
+  <si>
+    <t>id_guru</t>
   </si>
   <si>
     <t>PT Contoh Teknologi</t>
   </si>
   <si>
-    <t>Teknologi Informasi</t>
-  </si>
-  <si>
     <t>Jl. Merdeka No. 10</t>
   </si>
   <si>
     <t>0215551234</t>
   </si>
   <si>
-    <t>info@contoh.test</t>
+    <t>Budi Santoso</t>
   </si>
   <si>
     <t>CV Mitra Industri</t>
   </si>
   <si>
-    <t>Manufaktur</t>
-  </si>
-  <si>
     <t>Jl. Industri No. 5</t>
   </si>
   <si>
     <t>0225556789</t>
   </si>
   <si>
-    <t>kontak@mitra.test</t>
-  </si>
-  <si>
-    <t>Catatan: nama wajib diisi dan dipakai untuk mencocokkan data saat import.</t>
+    <t>Siti Rahmawati</t>
+  </si>
+  <si>
+    <t>Catatan: ganti contoh ID dengan ID jurusan dan guru yang aktif. Nama dipakai untuk mencocokkan data saat import.</t>
   </si>
 </sst>
 </file>
@@ -490,17 +487,18 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="true" style="0"/>
-    <col min="2" max="2" width="26" customWidth="true" style="0"/>
-    <col min="3" max="3" width="36" customWidth="true" style="0"/>
-    <col min="4" max="4" width="18" customWidth="true" style="0"/>
-    <col min="5" max="5" width="32" customWidth="true" style="0"/>
+    <col min="2" max="2" width="36" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18" customWidth="true" style="0"/>
+    <col min="4" max="4" width="26" customWidth="true" style="0"/>
+    <col min="5" max="5" width="18" customWidth="true" style="0"/>
+    <col min="6" max="6" width="18" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customHeight="1" ht="26">
+    <row r="1" spans="1:6" customHeight="1" ht="26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,8 +506,9 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" customHeight="1" ht="22">
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" customHeight="1" ht="22">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -517,15 +516,17 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" customHeight="1" ht="22">
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" customHeight="1" ht="22">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -541,25 +542,31 @@
       <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" customHeight="1" ht="30">
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" customHeight="1" ht="30">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" customHeight="1" ht="30">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" customHeight="1" ht="30">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -572,31 +579,36 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" customHeight="1" ht="30">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" customHeight="1" ht="30">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
